--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -887,7 +887,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.172.xlsx
@@ -416,14 +416,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y50"/>
+  <dimension ref="A1:Y51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,13 +431,13 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
-    <col width="29" customWidth="1" min="19" max="19"/>
+    <col width="60" customWidth="1" min="19" max="19"/>
     <col width="30" customWidth="1" min="20" max="20"/>
     <col width="29" customWidth="1" min="21" max="21"/>
     <col width="31" customWidth="1" min="22" max="22"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.172.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.22250\oocihm.22250.172.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0172.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.22250\0172.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr"/>
@@ -605,16 +605,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L4: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ORDERSâ€”Continued.</t>
+          <t>L45: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L8: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: ORDERSâ€”Continued.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]165</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]165</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L2: isolated marker/symbol line :: 165</t>
@@ -622,7 +626,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L32: symbol-only separator/garbage line :: . 105</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]165</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -632,7 +636,11 @@
         </is>
       </c>
       <c r="R2" s="1" t="inlineStr"/>
-      <c r="S2" s="1" t="inlineStr"/>
+      <c r="S2" s="1" t="inlineStr">
+        <is>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 105</t>
+        </is>
+      </c>
       <c r="T2" s="1" t="inlineStr"/>
       <c r="U2" s="1" t="inlineStr"/>
       <c r="V2" s="1" t="inlineStr"/>
@@ -653,7 +661,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>86</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -672,12 +680,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+559C CJK UNIFIED IDEOGRAPH-559C | isolated marker/symbol line :: 喜</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L28: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 86â€”87â€”122</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 105</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -689,7 +697,7 @@
       </c>
       <c r="O3" s="1" t="inlineStr">
         <is>
-          <t>L34: isolated marker/symbol line :: 111</t>
+          <t>L28: symbol-only separator/garbage line :: 86—87—122</t>
         </is>
       </c>
       <c r="P3" s="1" t="inlineStr"/>
@@ -735,12 +743,12 @@
       <c r="I4" s="1" t="inlineStr"/>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+2193 DOWNWARDS ARROW | isolated marker/symbol line :: ↓</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L30: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ 105</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 111</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -752,7 +760,7 @@
       </c>
       <c r="O4" s="1" t="inlineStr">
         <is>
-          <t>L36: symbol-only separator/garbage line :: . 111</t>
+          <t>L30: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line | line starts with punctuation glued to text :: • 105</t>
         </is>
       </c>
       <c r="P4" s="1" t="inlineStr"/>
@@ -794,12 +802,12 @@
       <c r="I5" s="1" t="inlineStr"/>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 3â€”104</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
@@ -811,7 +819,7 @@
       </c>
       <c r="O5" s="1" t="inlineStr">
         <is>
-          <t>L38: isolated marker/symbol line :: 94</t>
+          <t>L32: symbol-only separator/garbage line :: . 105</t>
         </is>
       </c>
       <c r="P5" s="1" t="inlineStr"/>
@@ -851,12 +859,12 @@
       <c r="G6" s="1" t="inlineStr"/>
       <c r="H6" s="1" t="inlineStr"/>
       <c r="I6" s="1" t="inlineStr"/>
-      <c r="J6" s="1" t="inlineStr"/>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L94: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 66â€”67</t>
-        </is>
-      </c>
+      <c r="J6" s="1" t="inlineStr">
+        <is>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
@@ -866,7 +874,7 @@
       </c>
       <c r="O6" s="1" t="inlineStr">
         <is>
-          <t>L40: isolated marker/symbol line :: 94</t>
+          <t>L34: isolated marker/symbol line :: 111</t>
         </is>
       </c>
       <c r="P6" s="1" t="inlineStr"/>
@@ -907,11 +915,7 @@
       <c r="H7" s="1" t="inlineStr"/>
       <c r="I7" s="1" t="inlineStr"/>
       <c r="J7" s="1" t="inlineStr"/>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 67â€”68</t>
-        </is>
-      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
@@ -921,7 +925,7 @@
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L48: isolated marker/symbol line :: 138</t>
+          <t>L36: symbol-only separator/garbage line :: . 111</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr"/>
@@ -962,11 +966,7 @@
       <c r="H8" s="1" t="inlineStr"/>
       <c r="I8" s="1" t="inlineStr"/>
       <c r="J8" s="1" t="inlineStr"/>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L99: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ . 111</t>
-        </is>
-      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="O8" s="1" t="inlineStr">
         <is>
-          <t>L50: isolated marker/symbol line :: 138</t>
+          <t>L38: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P8" s="1" t="inlineStr"/>
@@ -1017,11 +1017,7 @@
       <c r="H9" s="1" t="inlineStr"/>
       <c r="I9" s="1" t="inlineStr"/>
       <c r="J9" s="1" t="inlineStr"/>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
-        </is>
-      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
@@ -1031,7 +1027,7 @@
       </c>
       <c r="O9" s="1" t="inlineStr">
         <is>
-          <t>L53: isolated marker/symbol line :: 146</t>
+          <t>L40: isolated marker/symbol line :: 94</t>
         </is>
       </c>
       <c r="P9" s="1" t="inlineStr"/>
@@ -1057,12 +1053,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
           <t>4</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>12</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1072,11 +1068,7 @@
       <c r="H10" s="1" t="inlineStr"/>
       <c r="I10" s="1" t="inlineStr"/>
       <c r="J10" s="1" t="inlineStr"/>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L114: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 6â€”87</t>
-        </is>
-      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
@@ -1086,7 +1078,7 @@
       </c>
       <c r="O10" s="1" t="inlineStr">
         <is>
-          <t>L55: symbol-only separator/garbage line :: . 142</t>
+          <t>L46: symbol-only separator/garbage line :: 3—104</t>
         </is>
       </c>
       <c r="P10" s="1" t="inlineStr"/>
@@ -1113,7 +1105,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1123,11 +1115,7 @@
       <c r="H11" s="1" t="inlineStr"/>
       <c r="I11" s="1" t="inlineStr"/>
       <c r="J11" s="1" t="inlineStr"/>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L146: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 79â€”80â€”81</t>
-        </is>
-      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
@@ -1137,7 +1125,7 @@
       </c>
       <c r="O11" s="1" t="inlineStr">
         <is>
-          <t>L57: symbol-only separator/garbage line :: . 140</t>
+          <t>L48: isolated marker/symbol line :: 138</t>
         </is>
       </c>
       <c r="P11" s="1" t="inlineStr"/>
@@ -1159,12 +1147,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>50</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>32</t>
+          <t>43</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1174,11 +1162,7 @@
       <c r="H12" s="1" t="inlineStr"/>
       <c r="I12" s="1" t="inlineStr"/>
       <c r="J12" s="1" t="inlineStr"/>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L148: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . 82â€”83</t>
-        </is>
-      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
@@ -1188,7 +1172,7 @@
       </c>
       <c r="O12" s="1" t="inlineStr">
         <is>
-          <t>L63: isolated marker/symbol line :: 114</t>
+          <t>L50: isolated marker/symbol line :: 138</t>
         </is>
       </c>
       <c r="P12" s="1" t="inlineStr"/>
@@ -1225,11 +1209,7 @@
       <c r="H13" s="1" t="inlineStr"/>
       <c r="I13" s="1" t="inlineStr"/>
       <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L152: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: 5â€”6</t>
-        </is>
-      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
@@ -1239,7 +1219,7 @@
       </c>
       <c r="O13" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: %</t>
+          <t>L53: isolated marker/symbol line :: 146</t>
         </is>
       </c>
       <c r="P13" s="1" t="inlineStr"/>
@@ -1266,7 +1246,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1286,7 +1266,7 @@
       </c>
       <c r="O14" s="1" t="inlineStr">
         <is>
-          <t>L95: isolated marker/symbol line :: 68</t>
+          <t>L55: symbol-only separator/garbage line :: . 142</t>
         </is>
       </c>
       <c r="P14" s="1" t="inlineStr"/>
@@ -1333,7 +1313,7 @@
       </c>
       <c r="O15" s="1" t="inlineStr">
         <is>
-          <t>L101: isolated marker/symbol line :: 112</t>
+          <t>L57: symbol-only separator/garbage line :: . 140</t>
         </is>
       </c>
       <c r="P15" s="1" t="inlineStr"/>
@@ -1380,7 +1360,7 @@
       </c>
       <c r="O16" s="1" t="inlineStr">
         <is>
-          <t>L103: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L63: isolated marker/symbol line :: 114</t>
         </is>
       </c>
       <c r="P16" s="1" t="inlineStr"/>
@@ -1427,7 +1407,7 @@
       </c>
       <c r="O17" s="1" t="inlineStr">
         <is>
-          <t>L105: isolated marker/symbol line :: 110</t>
+          <t>L65: isolated marker/symbol line :: %</t>
         </is>
       </c>
       <c r="P17" s="1" t="inlineStr"/>
@@ -1462,7 +1442,7 @@
       </c>
       <c r="O18" s="1" t="inlineStr">
         <is>
-          <t>L107: isolated marker/symbol line :: .3</t>
+          <t>L94: symbol-only separator/garbage line :: 66—67</t>
         </is>
       </c>
       <c r="P18" s="1" t="inlineStr"/>
@@ -1497,7 +1477,7 @@
       </c>
       <c r="O19" s="1" t="inlineStr">
         <is>
-          <t>L109: symbol-only separator/garbage line :: 3-4</t>
+          <t>L95: isolated marker/symbol line :: 68</t>
         </is>
       </c>
       <c r="P19" s="1" t="inlineStr"/>
@@ -1532,7 +1512,7 @@
       </c>
       <c r="O20" s="1" t="inlineStr">
         <is>
-          <t>L111: isolated marker/symbol line :: - 8</t>
+          <t>L97: symbol-only separator/garbage line :: . 67—68</t>
         </is>
       </c>
       <c r="P20" s="1" t="inlineStr"/>
@@ -1562,12 +1542,12 @@
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L43: isolated marker/symbol line :: Â·</t>
+          <t>L43: isolated marker/symbol line :: ·</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
         <is>
-          <t>L112: isolated marker/symbol line :: 12</t>
+          <t>L99: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | symbol-only separator/garbage line :: • . 111</t>
         </is>
       </c>
       <c r="P21" s="1" t="inlineStr"/>
@@ -1602,7 +1582,7 @@
       </c>
       <c r="O22" s="1" t="inlineStr">
         <is>
-          <t>L115: isolated marker/symbol line :: 155</t>
+          <t>L101: isolated marker/symbol line :: 112</t>
         </is>
       </c>
       <c r="P22" s="1" t="inlineStr"/>
@@ -1632,12 +1612,12 @@
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L45: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN | isolated marker/symbol line :: â€¢</t>
+          <t>L45: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
         <is>
-          <t>L117: isolated marker/symbol line :: .9</t>
+          <t>L103: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | isolated marker/symbol line :: •</t>
         </is>
       </c>
       <c r="P23" s="1" t="inlineStr"/>
@@ -1672,7 +1652,7 @@
       </c>
       <c r="O24" s="1" t="inlineStr">
         <is>
-          <t>L118: isolated marker/symbol line :: 9</t>
+          <t>L105: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="P24" s="1" t="inlineStr"/>
@@ -1707,7 +1687,7 @@
       </c>
       <c r="O25" s="1" t="inlineStr">
         <is>
-          <t>L120: isolated marker/symbol line :: 105</t>
+          <t>L107: isolated marker/symbol line :: .3</t>
         </is>
       </c>
       <c r="P25" s="1" t="inlineStr"/>
@@ -1742,7 +1722,7 @@
       </c>
       <c r="O26" s="1" t="inlineStr">
         <is>
-          <t>L122: isolated marker/symbol line :: 116</t>
+          <t>L109: symbol-only separator/garbage line :: 3-4</t>
         </is>
       </c>
       <c r="P26" s="1" t="inlineStr"/>
@@ -1777,7 +1757,7 @@
       </c>
       <c r="O27" s="1" t="inlineStr">
         <is>
-          <t>L124: isolated marker/symbol line :: 107</t>
+          <t>L111: isolated marker/symbol line :: - 8</t>
         </is>
       </c>
       <c r="P27" s="1" t="inlineStr"/>
@@ -1807,12 +1787,12 @@
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L56: isolated marker/symbol line :: â†“</t>
+          <t>L55: stray/suspicious non-ASCII glyph(s): U+559C CJK UNIFIED IDEOGRAPH-559C | isolated marker/symbol line :: 喜</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
         <is>
-          <t>L125: symbol-only separator/garbage line :: . 107</t>
+          <t>L112: isolated marker/symbol line :: 12</t>
         </is>
       </c>
       <c r="P28" s="1" t="inlineStr"/>
@@ -1842,12 +1822,12 @@
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L58: isolated marker/symbol line :: 142</t>
+          <t>L56: stray/suspicious non-ASCII glyph(s): U+2193 DOWNWARDS ARROW | isolated marker/symbol line :: ↓</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
         <is>
-          <t>L127: isolated marker/symbol line :: 112</t>
+          <t>L114: symbol-only separator/garbage line :: 6—87</t>
         </is>
       </c>
       <c r="P29" s="1" t="inlineStr"/>
@@ -1877,12 +1857,12 @@
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L59: isolated marker/symbol line :: 114</t>
+          <t>L58: isolated marker/symbol line :: 142</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
         <is>
-          <t>L139: isolated marker/symbol line :: 105</t>
+          <t>L115: isolated marker/symbol line :: 155</t>
         </is>
       </c>
       <c r="P30" s="1" t="inlineStr"/>
@@ -1912,12 +1892,12 @@
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L60: isolated marker/symbol line :: 110</t>
+          <t>L59: isolated marker/symbol line :: 114</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
         <is>
-          <t>L141: isolated marker/symbol line :: 1</t>
+          <t>L117: isolated marker/symbol line :: .9</t>
         </is>
       </c>
       <c r="P31" s="1" t="inlineStr"/>
@@ -1947,12 +1927,12 @@
       <c r="M32" s="1" t="inlineStr"/>
       <c r="N32" s="1" t="inlineStr">
         <is>
-          <t>L61: isolated marker/symbol line :: . 3</t>
+          <t>L60: isolated marker/symbol line :: 110</t>
         </is>
       </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
-          <t>L143: isolated marker/symbol line :: 1</t>
+          <t>L118: isolated marker/symbol line :: 9</t>
         </is>
       </c>
       <c r="P32" s="1" t="inlineStr"/>
@@ -1982,12 +1962,12 @@
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr">
         <is>
-          <t>L62: symbol-only separator/garbage line :: 3-4</t>
+          <t>L61: isolated marker/symbol line :: . 3</t>
         </is>
       </c>
       <c r="O33" s="1" t="inlineStr">
         <is>
-          <t>L150: isolated marker/symbol line :: .2</t>
+          <t>L120: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="P33" s="1" t="inlineStr"/>
@@ -2017,10 +1997,14 @@
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr">
         <is>
-          <t>L63: symbol-only separator/garbage line :: 6-87</t>
-        </is>
-      </c>
-      <c r="O34" s="1" t="inlineStr"/>
+          <t>L62: symbol-only separator/garbage line :: 3-4</t>
+        </is>
+      </c>
+      <c r="O34" s="1" t="inlineStr">
+        <is>
+          <t>L122: isolated marker/symbol line :: 116</t>
+        </is>
+      </c>
       <c r="P34" s="1" t="inlineStr"/>
       <c r="Q34" s="1" t="inlineStr"/>
       <c r="R34" s="1" t="inlineStr"/>
@@ -2048,10 +2032,14 @@
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr">
         <is>
-          <t>L64: isolated marker/symbol line :: 155</t>
-        </is>
-      </c>
-      <c r="O35" s="1" t="inlineStr"/>
+          <t>L63: symbol-only separator/garbage line :: 6-87</t>
+        </is>
+      </c>
+      <c r="O35" s="1" t="inlineStr">
+        <is>
+          <t>L124: isolated marker/symbol line :: 107</t>
+        </is>
+      </c>
       <c r="P35" s="1" t="inlineStr"/>
       <c r="Q35" s="1" t="inlineStr"/>
       <c r="R35" s="1" t="inlineStr"/>
@@ -2079,10 +2067,14 @@
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr">
         <is>
-          <t>L65: isolated marker/symbol line :: 9</t>
-        </is>
-      </c>
-      <c r="O36" s="1" t="inlineStr"/>
+          <t>L64: isolated marker/symbol line :: 155</t>
+        </is>
+      </c>
+      <c r="O36" s="1" t="inlineStr">
+        <is>
+          <t>L125: symbol-only separator/garbage line :: . 107</t>
+        </is>
+      </c>
       <c r="P36" s="1" t="inlineStr"/>
       <c r="Q36" s="1" t="inlineStr"/>
       <c r="R36" s="1" t="inlineStr"/>
@@ -2110,10 +2102,14 @@
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr">
         <is>
-          <t>L67: isolated marker/symbol line :: 9</t>
-        </is>
-      </c>
-      <c r="O37" s="1" t="inlineStr"/>
+          <t>L65: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
+      <c r="O37" s="1" t="inlineStr">
+        <is>
+          <t>L127: isolated marker/symbol line :: 112</t>
+        </is>
+      </c>
       <c r="P37" s="1" t="inlineStr"/>
       <c r="Q37" s="1" t="inlineStr"/>
       <c r="R37" s="1" t="inlineStr"/>
@@ -2141,10 +2137,14 @@
       <c r="M38" s="1" t="inlineStr"/>
       <c r="N38" s="1" t="inlineStr">
         <is>
-          <t>L70: isolated marker/symbol line :: 107</t>
-        </is>
-      </c>
-      <c r="O38" s="1" t="inlineStr"/>
+          <t>L67: isolated marker/symbol line :: 9</t>
+        </is>
+      </c>
+      <c r="O38" s="1" t="inlineStr">
+        <is>
+          <t>L139: isolated marker/symbol line :: 105</t>
+        </is>
+      </c>
       <c r="P38" s="1" t="inlineStr"/>
       <c r="Q38" s="1" t="inlineStr"/>
       <c r="R38" s="1" t="inlineStr"/>
@@ -2172,10 +2172,14 @@
       <c r="M39" s="1" t="inlineStr"/>
       <c r="N39" s="1" t="inlineStr">
         <is>
-          <t>L72: isolated marker/symbol line :: 107</t>
-        </is>
-      </c>
-      <c r="O39" s="1" t="inlineStr"/>
+          <t>L70: isolated marker/symbol line :: 107</t>
+        </is>
+      </c>
+      <c r="O39" s="1" t="inlineStr">
+        <is>
+          <t>L141: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P39" s="1" t="inlineStr"/>
       <c r="Q39" s="1" t="inlineStr"/>
       <c r="R39" s="1" t="inlineStr"/>
@@ -2203,10 +2207,14 @@
       <c r="M40" s="1" t="inlineStr"/>
       <c r="N40" s="1" t="inlineStr">
         <is>
-          <t>L74: isolated marker/symbol line :: 112</t>
-        </is>
-      </c>
-      <c r="O40" s="1" t="inlineStr"/>
+          <t>L72: isolated marker/symbol line :: 107</t>
+        </is>
+      </c>
+      <c r="O40" s="1" t="inlineStr">
+        <is>
+          <t>L143: isolated marker/symbol line :: 1</t>
+        </is>
+      </c>
       <c r="P40" s="1" t="inlineStr"/>
       <c r="Q40" s="1" t="inlineStr"/>
       <c r="R40" s="1" t="inlineStr"/>
@@ -2234,10 +2242,14 @@
       <c r="M41" s="1" t="inlineStr"/>
       <c r="N41" s="1" t="inlineStr">
         <is>
-          <t>L81: symbol-only separator/garbage line :: 79-80-81</t>
-        </is>
-      </c>
-      <c r="O41" s="1" t="inlineStr"/>
+          <t>L74: isolated marker/symbol line :: 112</t>
+        </is>
+      </c>
+      <c r="O41" s="1" t="inlineStr">
+        <is>
+          <t>L146: symbol-only separator/garbage line :: 79—80—81</t>
+        </is>
+      </c>
       <c r="P41" s="1" t="inlineStr"/>
       <c r="Q41" s="1" t="inlineStr"/>
       <c r="R41" s="1" t="inlineStr"/>
@@ -2265,10 +2277,14 @@
       <c r="M42" s="1" t="inlineStr"/>
       <c r="N42" s="1" t="inlineStr">
         <is>
-          <t>L83: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="O42" s="1" t="inlineStr"/>
+          <t>L81: symbol-only separator/garbage line :: 79-80-81</t>
+        </is>
+      </c>
+      <c r="O42" s="1" t="inlineStr">
+        <is>
+          <t>L148: symbol-only separator/garbage line :: . 82—83</t>
+        </is>
+      </c>
       <c r="P42" s="1" t="inlineStr"/>
       <c r="Q42" s="1" t="inlineStr"/>
       <c r="R42" s="1" t="inlineStr"/>
@@ -2296,10 +2312,14 @@
       <c r="M43" s="1" t="inlineStr"/>
       <c r="N43" s="1" t="inlineStr">
         <is>
-          <t>L84: symbol-only separator/garbage line :: 82-83</t>
-        </is>
-      </c>
-      <c r="O43" s="1" t="inlineStr"/>
+          <t>L83: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="O43" s="1" t="inlineStr">
+        <is>
+          <t>L150: isolated marker/symbol line :: .2</t>
+        </is>
+      </c>
       <c r="P43" s="1" t="inlineStr"/>
       <c r="Q43" s="1" t="inlineStr"/>
       <c r="R43" s="1" t="inlineStr"/>
@@ -2327,10 +2347,14 @@
       <c r="M44" s="1" t="inlineStr"/>
       <c r="N44" s="1" t="inlineStr">
         <is>
-          <t>L85: isolated marker/symbol line :: 105</t>
-        </is>
-      </c>
-      <c r="O44" s="1" t="inlineStr"/>
+          <t>L84: symbol-only separator/garbage line :: 82-83</t>
+        </is>
+      </c>
+      <c r="O44" s="1" t="inlineStr">
+        <is>
+          <t>L152: symbol-only separator/garbage line :: 5—6</t>
+        </is>
+      </c>
       <c r="P44" s="1" t="inlineStr"/>
       <c r="Q44" s="1" t="inlineStr"/>
       <c r="R44" s="1" t="inlineStr"/>
@@ -2358,7 +2382,7 @@
       <c r="M45" s="1" t="inlineStr"/>
       <c r="N45" s="1" t="inlineStr">
         <is>
-          <t>L86: isolated marker/symbol line :: 116</t>
+          <t>L85: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="O45" s="1" t="inlineStr"/>
@@ -2389,7 +2413,7 @@
       <c r="M46" s="1" t="inlineStr"/>
       <c r="N46" s="1" t="inlineStr">
         <is>
-          <t>L87: isolated marker/symbol line :: 105</t>
+          <t>L86: isolated marker/symbol line :: 116</t>
         </is>
       </c>
       <c r="O46" s="1" t="inlineStr"/>
@@ -2420,7 +2444,7 @@
       <c r="M47" s="1" t="inlineStr"/>
       <c r="N47" s="1" t="inlineStr">
         <is>
-          <t>L88: isolated marker/symbol line :: 1</t>
+          <t>L87: isolated marker/symbol line :: 105</t>
         </is>
       </c>
       <c r="O47" s="1" t="inlineStr"/>
@@ -2451,7 +2475,7 @@
       <c r="M48" s="1" t="inlineStr"/>
       <c r="N48" s="1" t="inlineStr">
         <is>
-          <t>L89: isolated marker/symbol line :: . 2</t>
+          <t>L88: isolated marker/symbol line :: 1</t>
         </is>
       </c>
       <c r="O48" s="1" t="inlineStr"/>
@@ -2482,7 +2506,7 @@
       <c r="M49" s="1" t="inlineStr"/>
       <c r="N49" s="1" t="inlineStr">
         <is>
-          <t>L90: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L89: isolated marker/symbol line :: . 2</t>
         </is>
       </c>
       <c r="O49" s="1" t="inlineStr"/>
@@ -2513,7 +2537,7 @@
       <c r="M50" s="1" t="inlineStr"/>
       <c r="N50" s="1" t="inlineStr">
         <is>
-          <t>L91: symbol-only separator/garbage line :: 5-6</t>
+          <t>L90: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O50" s="1" t="inlineStr"/>
@@ -2528,6 +2552,37 @@
       <c r="X50" s="1" t="inlineStr"/>
       <c r="Y50" s="1" t="inlineStr"/>
     </row>
+    <row r="51">
+      <c r="A51" s="1" t="inlineStr"/>
+      <c r="B51" s="1" t="inlineStr"/>
+      <c r="C51" s="1" t="inlineStr"/>
+      <c r="D51" s="1" t="inlineStr"/>
+      <c r="E51" s="1" t="inlineStr"/>
+      <c r="F51" s="1" t="inlineStr"/>
+      <c r="G51" s="1" t="inlineStr"/>
+      <c r="H51" s="1" t="inlineStr"/>
+      <c r="I51" s="1" t="inlineStr"/>
+      <c r="J51" s="1" t="inlineStr"/>
+      <c r="K51" s="1" t="inlineStr"/>
+      <c r="L51" s="1" t="inlineStr"/>
+      <c r="M51" s="1" t="inlineStr"/>
+      <c r="N51" s="1" t="inlineStr">
+        <is>
+          <t>L91: symbol-only separator/garbage line :: 5-6</t>
+        </is>
+      </c>
+      <c r="O51" s="1" t="inlineStr"/>
+      <c r="P51" s="1" t="inlineStr"/>
+      <c r="Q51" s="1" t="inlineStr"/>
+      <c r="R51" s="1" t="inlineStr"/>
+      <c r="S51" s="1" t="inlineStr"/>
+      <c r="T51" s="1" t="inlineStr"/>
+      <c r="U51" s="1" t="inlineStr"/>
+      <c r="V51" s="1" t="inlineStr"/>
+      <c r="W51" s="1" t="inlineStr"/>
+      <c r="X51" s="1" t="inlineStr"/>
+      <c r="Y51" s="1" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
